--- a/programme/chair-sheets/S57.xlsx
+++ b/programme/chair-sheets/S57.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
   <si>
     <t xml:space="preserve">ICCCMLA 2026 - Session attendance and evaluation sheet</t>
   </si>
@@ -122,6 +122,12 @@
   </si>
   <si>
     <t xml:space="preserve">Seismic Behaviour Assessment of Soft-Storey RC Asymmetric Buildings with and without Masonry Infill Walls Across Indian Seismic Zones</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moved</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moved to Tue 6 Oct, Session 43, 12:37 IST - do not mark here</t>
   </si>
   <si>
     <t xml:space="preserve">11:36-11:48</t>
@@ -207,7 +213,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="@"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -267,6 +273,21 @@
       <charset val="1"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <strike val="true"/>
+      <sz val="10"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <i val="true"/>
       <sz val="9"/>
       <color rgb="FF555555"/>
@@ -275,7 +296,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -291,13 +312,19 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFEDEDED"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE3EFF7"/>
-        <bgColor rgb="FFCCFFFF"/>
+        <bgColor rgb="FFEDEDED"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEDEDED"/>
+        <bgColor rgb="FFE3EFF7"/>
       </patternFill>
     </fill>
   </fills>
@@ -350,7 +377,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="20">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -399,6 +426,26 @@
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -407,7 +454,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -437,7 +484,7 @@
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FFBFBFBF"/>
-      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FF7F7F7F"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FFFFF2CC"/>
@@ -455,7 +502,7 @@
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFEDEDED"/>
       <rgbColor rgb="FFCCFFCC"/>
       <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF99CCFF"/>
@@ -867,42 +914,46 @@
       <c r="L12" s="10"/>
     </row>
     <row r="13" customFormat="false" ht="35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="6" t="n">
+      <c r="A13" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="D13" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="E13" s="9"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="9"/>
-      <c r="J13" s="11" t="str">
+      <c r="E13" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="F13" s="16"/>
+      <c r="G13" s="12"/>
+      <c r="H13" s="12"/>
+      <c r="I13" s="12"/>
+      <c r="J13" s="12" t="str">
         <f aca="false">IF(COUNT(G13:I13)=0,"",SUM(G13:I13))</f>
         <v/>
       </c>
-      <c r="K13" s="9"/>
-      <c r="L13" s="10"/>
+      <c r="K13" s="12"/>
+      <c r="L13" s="16" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="n">
         <v>4</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E14" s="9"/>
       <c r="F14" s="10"/>
@@ -921,13 +972,13 @@
         <v>5</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E15" s="9"/>
       <c r="F15" s="10"/>
@@ -946,13 +997,13 @@
         <v>6</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E16" s="9"/>
       <c r="F16" s="10"/>
@@ -968,203 +1019,203 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C18" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D18" s="3"/>
-      <c r="E18" s="12" t="n">
-        <f aca="false">COUNTA(C11:C16)</f>
-        <v>6</v>
+      <c r="E18" s="17" t="n">
+        <f aca="false">COUNTA(C11:C16)-COUNTIF(E11:E16,"Moved")</f>
+        <v>5</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C19" s="3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D19" s="3"/>
-      <c r="E19" s="12" t="n">
+      <c r="E19" s="17" t="n">
         <f aca="false">COUNTIF(E11:E16,"Present")</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C20" s="3" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D20" s="3"/>
-      <c r="E20" s="12" t="n">
+      <c r="E20" s="17" t="n">
         <f aca="false">COUNTIF(E11:E16,"Late")</f>
         <v>0</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C21" s="3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D21" s="3"/>
-      <c r="E21" s="12" t="n">
+      <c r="E21" s="17" t="n">
         <f aca="false">COUNTIF(E11:E16,"Absent")</f>
         <v>0</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C22" s="3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D22" s="3"/>
-      <c r="E22" s="12" t="n">
+      <c r="E22" s="17" t="n">
         <f aca="false">COUNTA(C11:C16)-COUNTA(E11:E16)</f>
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C23" s="3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D23" s="3"/>
-      <c r="E23" s="12" t="n">
+      <c r="E23" s="17" t="n">
         <f aca="false">COUNTIF(K11:K16,"Yes")</f>
         <v>0</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
-      <c r="D25" s="13"/>
-      <c r="E25" s="13"/>
-      <c r="F25" s="13"/>
-      <c r="G25" s="13"/>
-      <c r="H25" s="13"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="18"/>
+      <c r="F25" s="18"/>
+      <c r="G25" s="18"/>
+      <c r="H25" s="18"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
-      <c r="D26" s="13"/>
-      <c r="E26" s="13"/>
-      <c r="F26" s="13"/>
-      <c r="G26" s="13"/>
-      <c r="H26" s="13"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="18"/>
+      <c r="F26" s="18"/>
+      <c r="G26" s="18"/>
+      <c r="H26" s="18"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
-      <c r="D27" s="13"/>
-      <c r="E27" s="13"/>
-      <c r="F27" s="13"/>
-      <c r="G27" s="13"/>
-      <c r="H27" s="13"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="18"/>
+      <c r="F27" s="18"/>
+      <c r="G27" s="18"/>
+      <c r="H27" s="18"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
-      <c r="D28" s="13"/>
-      <c r="E28" s="13"/>
-      <c r="F28" s="13"/>
-      <c r="G28" s="13"/>
-      <c r="H28" s="13"/>
+      <c r="D28" s="18"/>
+      <c r="E28" s="18"/>
+      <c r="F28" s="18"/>
+      <c r="G28" s="18"/>
+      <c r="H28" s="18"/>
     </row>
     <row r="29" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
-      <c r="D29" s="13"/>
-      <c r="E29" s="13"/>
-      <c r="F29" s="13"/>
-      <c r="G29" s="13"/>
-      <c r="H29" s="13"/>
+      <c r="D29" s="18"/>
+      <c r="E29" s="18"/>
+      <c r="F29" s="18"/>
+      <c r="G29" s="18"/>
+      <c r="H29" s="18"/>
     </row>
     <row r="31" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="14"/>
-      <c r="J31" s="14"/>
-      <c r="K31" s="14"/>
-      <c r="L31" s="14"/>
+      <c r="A31" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="B31" s="19"/>
+      <c r="C31" s="19"/>
+      <c r="D31" s="19"/>
+      <c r="E31" s="19"/>
+      <c r="F31" s="19"/>
+      <c r="G31" s="19"/>
+      <c r="H31" s="19"/>
+      <c r="I31" s="19"/>
+      <c r="J31" s="19"/>
+      <c r="K31" s="19"/>
+      <c r="L31" s="19"/>
     </row>
     <row r="32" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="14"/>
-      <c r="J32" s="14"/>
-      <c r="K32" s="14"/>
-      <c r="L32" s="14"/>
+      <c r="A32" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="B32" s="19"/>
+      <c r="C32" s="19"/>
+      <c r="D32" s="19"/>
+      <c r="E32" s="19"/>
+      <c r="F32" s="19"/>
+      <c r="G32" s="19"/>
+      <c r="H32" s="19"/>
+      <c r="I32" s="19"/>
+      <c r="J32" s="19"/>
+      <c r="K32" s="19"/>
+      <c r="L32" s="19"/>
     </row>
     <row r="33" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="14"/>
-      <c r="J33" s="14"/>
-      <c r="K33" s="14"/>
-      <c r="L33" s="14"/>
+      <c r="A33" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="B33" s="19"/>
+      <c r="C33" s="19"/>
+      <c r="D33" s="19"/>
+      <c r="E33" s="19"/>
+      <c r="F33" s="19"/>
+      <c r="G33" s="19"/>
+      <c r="H33" s="19"/>
+      <c r="I33" s="19"/>
+      <c r="J33" s="19"/>
+      <c r="K33" s="19"/>
+      <c r="L33" s="19"/>
     </row>
     <row r="34" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
-      <c r="I34" s="14"/>
-      <c r="J34" s="14"/>
-      <c r="K34" s="14"/>
-      <c r="L34" s="14"/>
+      <c r="A34" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="B34" s="19"/>
+      <c r="C34" s="19"/>
+      <c r="D34" s="19"/>
+      <c r="E34" s="19"/>
+      <c r="F34" s="19"/>
+      <c r="G34" s="19"/>
+      <c r="H34" s="19"/>
+      <c r="I34" s="19"/>
+      <c r="J34" s="19"/>
+      <c r="K34" s="19"/>
+      <c r="L34" s="19"/>
     </row>
     <row r="35" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="14" t="s">
-        <v>57</v>
-      </c>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14"/>
-      <c r="I35" s="14"/>
-      <c r="J35" s="14"/>
-      <c r="K35" s="14"/>
-      <c r="L35" s="14"/>
+      <c r="A35" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="B35" s="19"/>
+      <c r="C35" s="19"/>
+      <c r="D35" s="19"/>
+      <c r="E35" s="19"/>
+      <c r="F35" s="19"/>
+      <c r="G35" s="19"/>
+      <c r="H35" s="19"/>
+      <c r="I35" s="19"/>
+      <c r="J35" s="19"/>
+      <c r="K35" s="19"/>
+      <c r="L35" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="31">
